--- a/daily_matches/job_matches_2026-05-12.xlsx
+++ b/daily_matches/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Redshift, BigQuery, Synapse</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Redshift, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Databricks, Kafka, NoSQL</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Redshift, PostgreSQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (experienced level professional)</t>
+          <t>Sr JAVA Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Michelin</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Databricks, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af224ae3ea6d8dee</t>
+          <t>https://www.indeed.com/viewjob?jk=bd2c955fa8205fe8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (experienced level professional)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Michelin</t>
+          <t>SilverEdge Government Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Databricks, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=264fc6304851250e</t>
+          <t>https://www.indeed.com/viewjob?jk=8db426b190d5761e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer, East</t>
+          <t>Data Engineer II - AWS/PySpark/ETL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arize AI</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Kubernetes, Python</t>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3adbef2c1898008</t>
+          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, PostgreSQL, SQL, R</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,262 +766,367 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, BigQuery, CI/CD, Terraform, Snowflake, BigQuery, Python, R, Java</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Cortex, Data Lake, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4fac07af27a1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist (MMM)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19183e04db4cde34</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Founding Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, PyTorch, FastAPI, Docker, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c92f3b086f3ccfc</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SDET – QA Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, EC2, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba21f3c28fe3b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Junior Software Developer (RapidScale)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cox Communications Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f184e62d6665cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ab79a985d592d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Product Strategy Quant Analytics-Senior Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bay Lake, FL, US USA</t>
+          <t>Delaware, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15e4b9c5f386bee7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Research Engineer (Agentic systems, AI, Full-Stack)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8ea3e263de0bbe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Research Engineer (Agentic systems, AI, Full-Stack)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa2a2a75b8ff8230</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Itential</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Tableau, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3afb5f9090a1220f</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b76b47a4f1808d69</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-12.xlsx
+++ b/daily_matches/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, PySpark, ETL, AWS</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Redshift, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, S3, Data Lake, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e01551f023130f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8cbd0914920ce275</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>SquareTrade</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bbee41696a537c3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr JAVA Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd2c955fa8205fe8</t>
+          <t>https://www.indeed.com/viewjob?jk=66bb872d34439954</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SilverEdge Government Solutions</t>
+          <t>OrthoIllinois</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Elgin, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db426b190d5761e</t>
+          <t>https://www.indeed.com/viewjob?jk=552cbf37640b6701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c208f65820392c92</t>
+          <t>https://www.indeed.com/viewjob?jk=615e960b070945b2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ffdfcfe65c8757</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer – Physical AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Goddard Technologies, Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,392 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Product Strategy Quant Analytics-Senior Associate</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Delaware, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15e4b9c5f386bee7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Research Engineer (Agentic systems, AI, Full-Stack)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ea3e263de0bbe8</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Research Engineer (Agentic systems, AI, Full-Stack)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2a2a75b8ff8230</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Itential</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b76b47a4f1808d69</t>
+          <t>https://www.indeed.com/viewjob?jk=5b61a110081ea1f4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-12.xlsx
+++ b/daily_matches/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Senior AWS/Cloud Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, S3, Data Lake, FastAPI, Docker, Kubernetes</t>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cbd0914920ce275</t>
+          <t>https://www.indeed.com/viewjob?jk=9b81fafe10b8ad51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python/GenAI Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SquareTrade</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python</t>
+          <t>Generative AI, RAG, Copilot, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bbee41696a537c3</t>
+          <t>https://www.indeed.com/viewjob?jk=95d25e5f8678b9d6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior PHP / Laravel Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lendzi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Git, Snowflake, Databricks</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, EC2, CI/CD, GitHub Actions, Git, MySQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
+          <t>https://www.indeed.com/viewjob?jk=f530dda56359ff37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Juncos, PR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, OpenCV, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bb872d34439954</t>
+          <t>https://www.indeed.com/viewjob?jk=1aa18d2ae9d86bb2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>QA Test Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OrthoIllinois</t>
+          <t>RightEye</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Elgin, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python</t>
+          <t>Prompt Engineering, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552cbf37640b6701</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd26ece4523f804</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615e960b070945b2</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Scientist, Modeler</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Teleflora</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ffdfcfe65c8757</t>
+          <t>https://www.indeed.com/viewjob?jk=191c18e753c1628f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer – Physical AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Goddard Technologies, Inc</t>
+          <t>Relative Dynamics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,357 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b61a110081ea1f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd121a8b7a055bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Solutions Engineer | East Coast - Remote</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a46087e24f48d36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Solutions Engineer | East Coast - Remote</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07e0067f83cc755</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Solutions Engineer | East Coast - Remote</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68ebf5a44d3b48b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Solutions Engineer | West Coast - Remote</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7d9a6dece2d0415</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vforce Infotech</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9aa6c4d6257a9c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Prompt Engineer (AI Strategy &amp; Analytics)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10742ca97436c415</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UI/UX Engineer II, Software 1-3 years</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91e29a9ba9038548</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Privacy &amp; Governance</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacers Sports &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Analytics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacers Sports &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2c658434270a80f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist - Clinical AI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Johns Hopkins Health System</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Azure ML, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcbf2ece83437336</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-12.xlsx
+++ b/daily_matches/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AWS/Cloud Full Stack Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Lightspeed DMS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b81fafe10b8ad51</t>
+          <t>https://www.indeed.com/viewjob?jk=790fd744b846b460</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python/GenAI Solutions Architect</t>
+          <t>Senior Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Telnyx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
+          <t>Athena, BigQuery, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d25e5f8678b9d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c6a757ac0ad5e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior PHP / Laravel Engineer</t>
+          <t>Software Engineer (Apps &amp; Firmware)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lendzi</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, EC2, CI/CD, GitHub Actions, Git, MySQL, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Redshift, Kubernetes, Git, Redshift, Kafka, MySQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f530dda56359ff37</t>
+          <t>https://www.indeed.com/viewjob?jk=292176db93d28a70</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Juncos, PR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, OpenCV, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aa18d2ae9d86bb2</t>
+          <t>https://www.indeed.com/viewjob?jk=e54fee3b343655bb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QA Test Engineer</t>
+          <t>Developer (Java Full Stack)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RightEye</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prompt Engineering, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd26ece4523f804</t>
+          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Git, Kafka, MongoDB, Cassandra, NoSQL, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=0b3f05e86ef2713f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist, Modeler</t>
+          <t>IT Solutions Engineer / Analyst II | Palo Verde</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Teleflora</t>
+          <t>Arizona Public Service (APS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tonopah, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, FastAPI, Docker, Kubernetes, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c18e753c1628f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc49f370db66ef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Yodlee Engineering Summer Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Relative Dynamics</t>
+          <t>Yodlee</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, FastAPI, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd121a8b7a055bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0d384b7f844ffb11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer | East Coast - Remote</t>
+          <t>Senior Application Security Tester &amp; AI Red Team Subject Matter Expert</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>Evolve Security</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Pinecone, AKS, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a46087e24f48d36</t>
+          <t>https://www.indeed.com/viewjob?jk=30eddfaa0a6048dc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer | East Coast - Remote</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, S3, EC2, Glue, CI/CD, Snowflake, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07e0067f83cc755</t>
+          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer | East Coast - Remote</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ebf5a44d3b48b1</t>
+          <t>https://www.indeed.com/viewjob?jk=db457a389924906f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer | West Coast - Remote</t>
+          <t>Software Development Engineer III, Popeyes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d9a6dece2d0415</t>
+          <t>https://www.indeed.com/viewjob?jk=8f92bedd062803af</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Git, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,182 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9aa6c4d6257a9c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Prompt Engineer (AI Strategy &amp; Analytics)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S R International Inc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10742ca97436c415</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>UI/UX Engineer II, Software 1-3 years</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>FIS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91e29a9ba9038548</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Privacy &amp; Governance</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Pacers Sports &amp; Entertainment</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Analytics</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Pacers Sports &amp; Entertainment</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c658434270a80f</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist - Clinical AI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Johns Hopkins Health System</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Azure ML, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcbf2ece83437336</t>
+          <t>https://www.indeed.com/viewjob?jk=b156ccfbb74fffe5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-12.xlsx
+++ b/daily_matches/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lightspeed DMS</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>S3, Glue, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790fd744b846b460</t>
+          <t>https://www.indeed.com/viewjob?jk=7b20e14df8f336ad</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python)</t>
+          <t>Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Telnyx</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athena, BigQuery, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, BigQuery, PostgreSQL</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c6a757ac0ad5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=42abb3669a21c76a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer (Apps &amp; Firmware)</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Redshift, Kubernetes, Git, Redshift, Kafka, MySQL, Python</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Cortex, Redshift, BigQuery, Data Lake, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292176db93d28a70</t>
+          <t>https://www.indeed.com/viewjob?jk=40882caab5cfe429</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, MySQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e54fee3b343655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=04ba2a6552a27cbb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Developer (Java Full Stack)</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>POWERX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, NoSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, S3, EC2, Git, PostgreSQL, MySQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Git, Kafka, MongoDB, Cassandra, NoSQL, Tableau, Python, SQL, R</t>
+          <t>RAG, BigQuery, Kubernetes, Terraform, Git, Snowflake, BigQuery, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3f05e86ef2713f</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT Solutions Engineer / Analyst II | Palo Verde</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arizona Public Service (APS)</t>
+          <t>Compotech, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tonopah, AZ, US USA</t>
+          <t>Orono, ME, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, FastAPI, Docker, Kubernetes, Git, Python, R</t>
+          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc49f370db66ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e51c6d9aa1eec7c5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yodlee Engineering Summer Intern</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yodlee</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, FastAPI, Git, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Power BI, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d384b7f844ffb11</t>
+          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Application Security Tester &amp; AI Red Team Subject Matter Expert</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Evolve Security</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Pinecone, AKS, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Power BI, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30eddfaa0a6048dc</t>
+          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Glue, CI/CD, Snowflake, Python, R, Java, Scala</t>
+          <t>RAG, S3, Redshift, CI/CD, Snowflake, Databricks, Redshift, Tableau, Power BI, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MNTN</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,77 +846,427 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db457a389924906f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b780cbd54e20e82</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Development Engineer III, Popeyes</t>
+          <t>AI Full Stack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>Obra Capital, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, FastAPI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f92bedd062803af</t>
+          <t>https://www.indeed.com/viewjob?jk=f0edcfb77ae6a295</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Application Security Tester &amp; AI Red Team Subject Matter Expert</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Evolve Security</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Copilot, Pinecone, AKS, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b48a3baf20d934bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Global Banking &amp; Markets, Securities Settlement Engineering</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afcab31fabe71ed5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LVT (LiveView Technologies)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>American Fork, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfd0bd18b7983667</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dentsu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, MongoDB, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3883bb1e0ff09052</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mad Mobile</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Git, Hadoop, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b156ccfbb74fffe5</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b991d4d924d1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Popeyes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Popeyes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Financial Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cpg.io eCommerce Distributors</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Addison, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PostgreSQL, MySQL, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Centennial, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b633cc5be11d0f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Cloud Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lunar Outpost</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6e93991e1b78bb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bay Lake, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0054a3bf0379bfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior AI-Product Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mitratech</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd6a32a276e56fe</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-12.xlsx
+++ b/daily_matches/job_matches_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Python Engineer with REST &amp; GenAI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Redshift</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b20e14df8f336ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dev Ops Engineer</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>LangChain, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42abb3669a21c76a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Cortex, Redshift, BigQuery, Data Lake, Snowflake, BigQuery</t>
+          <t>LangChain, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40882caab5cfe429</t>
+          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python</t>
+          <t>Generative AI, RAG, Gemini, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ba2a6552a27cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=8348059168d7d3ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POWERX</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, EC2, Git, PostgreSQL, MySQL, MongoDB, Python</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3c372f8cf8158e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer (Python, Kafka / Confluent)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, Terraform, Git, Snowflake, BigQuery, Kafka, PostgreSQL, Python</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Golang Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compotech, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orono, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51c6d9aa1eec7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=27afc7879d2cdd98</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Power BI, SQL</t>
+          <t>RAG, Copilot, Cortex, Git, Snowflake, Databricks, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
+          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Power BI, SQL</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=66548b5b80ae2773</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Technical Product Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, CI/CD, Snowflake, Databricks, Redshift, Tableau, Power BI, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=a26388b5e9669b0d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b780cbd54e20e82</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer</t>
+          <t>AI Engineer - Onsite</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Obra Capital, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,29 +871,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, FastAPI, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, S3, Docker, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0edcfb77ae6a295</t>
+          <t>https://www.indeed.com/viewjob?jk=3fdebe4c32cf8036</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Application Security Tester &amp; AI Red Team Subject Matter Expert</t>
+          <t>Infrastructure Operations Engineer Texas (Ward County)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Evolve Security</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,46 +902,46 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Pinecone, AKS, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48a3baf20d934bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4c280dcaffde51ca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Global Banking &amp; Markets, Securities Settlement Engineering</t>
+          <t>Infrastructure Operations Engineer (North Carolina)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcab31fabe71ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad490bf0370bc558</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Internship – Artificial Intelligence</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>APM Terminals</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd0bd18b7983667</t>
+          <t>https://www.indeed.com/viewjob?jk=350077045b72bd49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Machine Learning Engineer/Senior Machine Learning Engineer - Infra</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, MongoDB, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, S3, EC2, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3883bb1e0ff09052</t>
+          <t>https://www.indeed.com/viewjob?jk=608eb03f51b34fa3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer, Vehicle Fulfillment Experience</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mad Mobile</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b991d4d924d1260</t>
+          <t>https://www.indeed.com/viewjob?jk=4a84c904dc66baf4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Snowflake, Tableau, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=d223de3780baad86</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Financial Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cpg.io eCommerce Distributors</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Addison, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PostgreSQL, MySQL, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+          <t>https://www.indeed.com/viewjob?jk=0116487b900524c2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, Databricks, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b633cc5be11d0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lunar Outpost</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Optimization</t>
+          <t>Generative AI, RAG, Gemini, S3, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e93991e1b78bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fc364bd1ad60dd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>GenAI Application Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bay Lake, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Git, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0054a3bf0379bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=241913635dfbf4ea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI-Product Engineer</t>
+          <t>Java API Engineer - AWS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, S3, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,252 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd6a32a276e56fe</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7ba4ea446a717</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Java API Engineer - AWS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35b25a76cd805638</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Technical Architect - Oracle Fusion Applications</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Acuity Inc.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ontario, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e99fe4ff53e086</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (part-time)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LinTech Global, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2caf114aab2c3a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist, New College Grad - 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79f6f3749f4c84d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst (Project Hire/Internal Assignment)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lake Buena Vista, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Kubernetes, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02da5d670bf7cb33</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate - Consumer Bank Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a040ce6e1e10915</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Blattner Company</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, XGBoost, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fda02efebaee7110</t>
         </is>
       </c>
     </row>
